--- a/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2016_T1_0.xlsx
+++ b/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2016_T1_0.xlsx
@@ -57,7 +57,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>93</t>
+    <t>89</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -69,64 +69,64 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>1.004</t>
-  </si>
-  <si>
-    <t>(0.173)</t>
-  </si>
-  <si>
-    <t>5.527</t>
-  </si>
-  <si>
-    <t>(0.749)</t>
-  </si>
-  <si>
-    <t>33.389</t>
-  </si>
-  <si>
-    <t>(7.658)</t>
-  </si>
-  <si>
-    <t>39.796</t>
-  </si>
-  <si>
-    <t>(9.011)</t>
-  </si>
-  <si>
-    <t>1.354</t>
-  </si>
-  <si>
-    <t>(0.213)</t>
-  </si>
-  <si>
-    <t>7.204</t>
-  </si>
-  <si>
-    <t>(0.817)</t>
-  </si>
-  <si>
-    <t>3.468</t>
-  </si>
-  <si>
-    <t>(1.686)</t>
-  </si>
-  <si>
-    <t>0.581</t>
-  </si>
-  <si>
-    <t>(0.103)</t>
-  </si>
-  <si>
-    <t>42.115</t>
-  </si>
-  <si>
-    <t>(7.362)</t>
-  </si>
-  <si>
-    <t>38.674</t>
-  </si>
-  <si>
-    <t>(15.152)</t>
+    <t>1.049</t>
+  </si>
+  <si>
+    <t>(0.179)</t>
+  </si>
+  <si>
+    <t>5.775</t>
+  </si>
+  <si>
+    <t>(0.773)</t>
+  </si>
+  <si>
+    <t>24.520</t>
+  </si>
+  <si>
+    <t>(4.525)</t>
+  </si>
+  <si>
+    <t>28.889</t>
+  </si>
+  <si>
+    <t>(4.786)</t>
+  </si>
+  <si>
+    <t>1.255</t>
+  </si>
+  <si>
+    <t>(0.166)</t>
+  </si>
+  <si>
+    <t>7.517</t>
+  </si>
+  <si>
+    <t>(0.839)</t>
+  </si>
+  <si>
+    <t>1.484</t>
+  </si>
+  <si>
+    <t>(0.207)</t>
+  </si>
+  <si>
+    <t>0.582</t>
+  </si>
+  <si>
+    <t>(0.106)</t>
+  </si>
+  <si>
+    <t>37.731</t>
+  </si>
+  <si>
+    <t>(6.143)</t>
+  </si>
+  <si>
+    <t>20.406</t>
+  </si>
+  <si>
+    <t>(3.509)</t>
   </si>
   <si>
     <t>21</t>
@@ -198,7 +198,7 @@
     <t>(9.280)</t>
   </si>
   <si>
-    <t>114</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -210,34 +210,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>-0.101</t>
-  </si>
-  <si>
-    <t>-0.622</t>
-  </si>
-  <si>
-    <t>21.583</t>
-  </si>
-  <si>
-    <t>19.455</t>
-  </si>
-  <si>
-    <t>-0.032</t>
-  </si>
-  <si>
-    <t>-1.157</t>
-  </si>
-  <si>
-    <t>-1.818</t>
-  </si>
-  <si>
-    <t>-0.177</t>
-  </si>
-  <si>
-    <t>34.766**</t>
-  </si>
-  <si>
-    <t>4.126</t>
+    <t>-0.146</t>
+  </si>
+  <si>
+    <t>-0.871</t>
+  </si>
+  <si>
+    <t>30.453***</t>
+  </si>
+  <si>
+    <t>30.363***</t>
+  </si>
+  <si>
+    <t>0.067</t>
+  </si>
+  <si>
+    <t>-1.469</t>
+  </si>
+  <si>
+    <t>0.166</t>
+  </si>
+  <si>
+    <t>-0.178</t>
+  </si>
+  <si>
+    <t>39.149***</t>
+  </si>
+  <si>
+    <t>22.395***</t>
   </si>
 </sst>
 </file>
